--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20242025.xlsx
@@ -1132,7 +1132,7 @@
         <v>2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.23</v>
+        <v>1</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -2655,7 +2655,7 @@
         <v>1</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ10" t="n">
         <v>1.5</v>
@@ -5056,7 +5056,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.23</v>
+        <v>1</v>
       </c>
       <c r="AR21" t="n">
         <v>2</v>
@@ -7887,7 +7887,7 @@
         <v>0.5</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ34" t="n">
         <v>2</v>
@@ -8108,7 +8108,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.23</v>
+        <v>1</v>
       </c>
       <c r="AR35" t="n">
         <v>1.8</v>
@@ -9013,10 +9013,10 @@
         <v>4</v>
       </c>
       <c r="BB39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD39" t="n">
         <v>2.55</v>
@@ -9228,13 +9228,13 @@
         <v>5</v>
       </c>
       <c r="BA40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB40" t="n">
         <v>3</v>
       </c>
       <c r="BC40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD40" t="n">
         <v>1.81</v>
@@ -10506,7 +10506,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.23</v>
+        <v>1</v>
       </c>
       <c r="AR46" t="n">
         <v>1.53</v>
@@ -10939,7 +10939,7 @@
         <v>3</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ48" t="n">
         <v>2</v>
@@ -13558,7 +13558,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.23</v>
+        <v>1</v>
       </c>
       <c r="AR60" t="n">
         <v>1.32</v>
@@ -14427,7 +14427,7 @@
         <v>1.5</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ64" t="n">
         <v>1</v>
@@ -15735,7 +15735,7 @@
         <v>2.17</v>
       </c>
       <c r="AP70" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ70" t="n">
         <v>1.71</v>
@@ -16825,10 +16825,10 @@
         <v>0.4</v>
       </c>
       <c r="AP75" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.23</v>
+        <v>1</v>
       </c>
       <c r="AR75" t="n">
         <v>1.66</v>
@@ -18790,7 +18790,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ84" t="n">
-        <v>1.23</v>
+        <v>1</v>
       </c>
       <c r="AR84" t="n">
         <v>1.77</v>
@@ -22060,7 +22060,7 @@
         <v>0.85</v>
       </c>
       <c r="AQ99" t="n">
-        <v>1.23</v>
+        <v>1</v>
       </c>
       <c r="AR99" t="n">
         <v>0.85</v>
@@ -22810,7 +22810,7 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>45696.23958333334</v>
+        <v>45696.23263888889</v>
       </c>
       <c r="F103" t="n">
         <v>18</v>
@@ -22944,22 +22944,22 @@
         <v>3.24</v>
       </c>
       <c r="AU103" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV103" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AW103" t="n">
         <v>13</v>
       </c>
       <c r="AX103" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AY103" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ103" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA103" t="n">
         <v>10</v>
@@ -23583,7 +23583,7 @@
         <v>0.86</v>
       </c>
       <c r="AP106" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ106" t="n">
         <v>0.6899999999999999</v>
@@ -24458,7 +24458,7 @@
         <v>0.92</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1.23</v>
+        <v>1</v>
       </c>
       <c r="AR110" t="n">
         <v>1.38</v>
@@ -24900,10 +24900,10 @@
         <v>1.15</v>
       </c>
       <c r="AS112" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AT112" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="AU112" t="n">
         <v>3</v>
@@ -27071,7 +27071,7 @@
         <v>1.78</v>
       </c>
       <c r="AP122" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ122" t="n">
         <v>1.77</v>
@@ -27292,7 +27292,7 @@
         <v>1.31</v>
       </c>
       <c r="AQ123" t="n">
-        <v>1.23</v>
+        <v>1</v>
       </c>
       <c r="AR123" t="n">
         <v>1.51</v>
@@ -28161,19 +28161,19 @@
         <v>1.44</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ127" t="n">
         <v>1.38</v>
       </c>
       <c r="AR127" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="AS127" t="n">
         <v>1.18</v>
       </c>
       <c r="AT127" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="AU127" t="n">
         <v>8</v>
@@ -28388,10 +28388,10 @@
         <v>1.5</v>
       </c>
       <c r="AS128" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="AT128" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="AU128" t="n">
         <v>8</v>
@@ -28818,7 +28818,7 @@
         <v>0.62</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.23</v>
+        <v>1</v>
       </c>
       <c r="AR130" t="n">
         <v>1.16</v>
@@ -29475,13 +29475,13 @@
         <v>1</v>
       </c>
       <c r="AR133" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AS133" t="n">
         <v>0.85</v>
       </c>
       <c r="AT133" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AU133" t="n">
         <v>7</v>
@@ -29914,10 +29914,10 @@
         <v>0.85</v>
       </c>
       <c r="AS135" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AT135" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="AU135" t="n">
         <v>4</v>
@@ -30129,13 +30129,13 @@
         <v>1.79</v>
       </c>
       <c r="AR136" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AS136" t="n">
         <v>1.36</v>
       </c>
       <c r="AT136" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="AU136" t="n">
         <v>8</v>
@@ -31004,10 +31004,10 @@
         <v>1.38</v>
       </c>
       <c r="AS140" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AT140" t="n">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="AU140" t="n">
         <v>4</v>
@@ -31222,10 +31222,10 @@
         <v>1.61</v>
       </c>
       <c r="AS141" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AT141" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="AU141" t="n">
         <v>4</v>
@@ -31431,19 +31431,19 @@
         <v>1.36</v>
       </c>
       <c r="AP142" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ142" t="n">
         <v>1.15</v>
       </c>
       <c r="AR142" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AS142" t="n">
         <v>1.06</v>
       </c>
       <c r="AT142" t="n">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="AU142" t="n">
         <v>5</v>
@@ -32203,28 +32203,28 @@
         <v>0</v>
       </c>
       <c r="J146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N146" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['57', '61', '85']</t>
         </is>
       </c>
       <c r="P146" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>['9', '69']</t>
         </is>
       </c>
       <c r="Q146" t="n">
@@ -32303,19 +32303,19 @@
         <v>0.91</v>
       </c>
       <c r="AP146" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ146" t="n">
-        <v>1.23</v>
+        <v>1</v>
       </c>
       <c r="AR146" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AS146" t="n">
         <v>1.16</v>
       </c>
       <c r="AT146" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="AU146" t="n">
         <v>7</v>
@@ -32324,13 +32324,13 @@
         <v>2</v>
       </c>
       <c r="AW146" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX146" t="n">
         <v>1</v>
       </c>
       <c r="AY146" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ146" t="n">
         <v>3</v>
@@ -32745,13 +32745,13 @@
         <v>2</v>
       </c>
       <c r="AR148" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AS148" t="n">
         <v>1.41</v>
       </c>
       <c r="AT148" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="AU148" t="n">
         <v>5</v>
@@ -34489,13 +34489,13 @@
         <v>1.38</v>
       </c>
       <c r="AR156" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AS156" t="n">
         <v>1.17</v>
       </c>
       <c r="AT156" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="AU156" t="n">
         <v>6</v>
@@ -34710,10 +34710,10 @@
         <v>1.27</v>
       </c>
       <c r="AS157" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AT157" t="n">
-        <v>2.65</v>
+        <v>2.58</v>
       </c>
       <c r="AU157" t="n">
         <v>7</v>
@@ -35785,25 +35785,25 @@
         <v>2.25</v>
       </c>
       <c r="AN162" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="AO162" t="n">
         <v>1.67</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ162" t="n">
         <v>1.5</v>
       </c>
       <c r="AR162" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AS162" t="n">
         <v>1.49</v>
       </c>
       <c r="AT162" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AU162" t="n">
         <v>6</v>
@@ -36442,13 +36442,13 @@
         <v>0.92</v>
       </c>
       <c r="AO165" t="n">
-        <v>1.08</v>
+        <v>0.83</v>
       </c>
       <c r="AP165" t="n">
         <v>0.85</v>
       </c>
       <c r="AQ165" t="n">
-        <v>1.23</v>
+        <v>1</v>
       </c>
       <c r="AR165" t="n">
         <v>1.29</v>
@@ -36657,25 +36657,25 @@
         <v>1.85</v>
       </c>
       <c r="AN166" t="n">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AO166" t="n">
         <v>1.33</v>
       </c>
       <c r="AP166" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AQ166" t="n">
         <v>1.23</v>
       </c>
       <c r="AR166" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AS166" t="n">
         <v>1.68</v>
       </c>
       <c r="AT166" t="n">
-        <v>3.64</v>
+        <v>3.59</v>
       </c>
       <c r="AU166" t="n">
         <v>9</v>
@@ -38186,22 +38186,22 @@
         <v>1.85</v>
       </c>
       <c r="AO173" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AP173" t="n">
         <v>1.76</v>
       </c>
       <c r="AQ173" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AR173" t="n">
         <v>1.56</v>
       </c>
       <c r="AS173" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AT173" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="AU173" t="n">
         <v>4</v>
@@ -38422,22 +38422,22 @@
         <v>3.22</v>
       </c>
       <c r="AU174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV174" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AW174" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AX174" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AY174" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ174" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA174" t="n">
         <v>9</v>
@@ -38631,31 +38631,31 @@
         <v>1.63</v>
       </c>
       <c r="AR175" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AS175" t="n">
         <v>1.66</v>
       </c>
       <c r="AT175" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="AU175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV175" t="n">
         <v>2</v>
       </c>
       <c r="AW175" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX175" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY175" t="n">
         <v>11</v>
       </c>
       <c r="AZ175" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA175" t="n">
         <v>7</v>
@@ -38837,25 +38837,25 @@
         <v>1.83</v>
       </c>
       <c r="AN176" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="AO176" t="n">
         <v>1.79</v>
       </c>
       <c r="AP176" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AQ176" t="n">
         <v>1.76</v>
       </c>
       <c r="AR176" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AS176" t="n">
         <v>1.55</v>
       </c>
       <c r="AT176" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="AU176" t="n">
         <v>7</v>
@@ -39055,25 +39055,25 @@
         <v>1.75</v>
       </c>
       <c r="AN177" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="AO177" t="n">
         <v>1.69</v>
       </c>
       <c r="AP177" t="n">
-        <v>1.79</v>
+        <v>1.9</v>
       </c>
       <c r="AQ177" t="n">
         <v>1.63</v>
       </c>
       <c r="AR177" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AS177" t="n">
         <v>1.65</v>
       </c>
       <c r="AT177" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="AU177" t="n">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados/Australia A-League_20242025.xlsx
@@ -22810,7 +22810,7 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>45696.23263888889</v>
+        <v>45696.23958333334</v>
       </c>
       <c r="F103" t="n">
         <v>18</v>
